--- a/task_submission/3.1_性能自验证报告.xlsx
+++ b/task_submission/3.1_性能自验证报告.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>96818d4f</t>
+          <t>72bb444f</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -926,7 +926,7 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>说明：官方模板「TBE算子性能」列，本算子无 TBE，改填任务书 Paged Full-QK 标杆(us)；「Ascend C算子性能」填 msprof task_time 均值。复现：msprof --ai-core=on --task-time=on --application="/root/backup/bench_aclnn_perf &lt;case&gt;"；chrono 对照 /root/backup/bench_aclnn_perf。仓分支 feat/turbo_quant_attention_score commit 96818d4f。截图粘贴到「Ascend截图」列。</t>
+          <t>说明：官方模板「TBE算子性能」列，本算子无 TBE，改填任务书 Paged Full-QK 标杆(us)；「Ascend C算子性能」填 msprof task_time 均值。复现：msprof --ai-core=on --task-time=on --application="/root/backup/bench_aclnn_perf &lt;case&gt;"；chrono 对照 /root/backup/bench_aclnn_perf。仓分支 feat/turbo_quant_attention_score commit 72bb444f。截图粘贴到「Ascend截图」列。</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -939,14 +939,6 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:J1"/>

--- a/task_submission/3.1_性能自验证报告.xlsx
+++ b/task_submission/3.1_性能自验证报告.xlsx
@@ -26,21 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -57,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,39 +71,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -117,8 +89,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,6 +164,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="2181225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,19 +510,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -517,7 +543,7 @@
           <t>TurboQuantAttentionScore</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>硬件型号</t>
@@ -528,7 +554,7 @@
           <t>Ascend 910B3（Atlas 800T A2）</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CANN版本</t>
@@ -539,8 +565,8 @@
           <t>9.1.0</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -553,7 +579,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>代码提交</t>
@@ -561,10 +587,10 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>72bb444f</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
+          <t>9c168855</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Golden</t>
@@ -572,13 +598,13 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>CPU 参考（与 tests/pytest/golden.py 同公式；本算子无 TBE）</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>CPU 参考（与 golden.py 同公式；本算子无 TBE）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>用例</t>
@@ -611,7 +637,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Paged Full-QK标杆(us)</t>
+          <t>TBE算子性能(us)/Full-QK标杆</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -630,7 +656,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TC_PF_001 / gqa_decode_kv4k</t>
@@ -658,7 +684,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_msprof_gqa_decode_kv4k.png</t>
+          <t>见嵌入图 / figures/perf_msprof_gqa_decode_kv4k.png</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
@@ -669,16 +695,16 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>对照为任务书 Paged Full-QK（非 TBE）。msprof task_time：预热10+采样60+去10大；ratio=0.776≤1.2。chrono=1189.042us。</t>
+          <t>msprof task_time（预热10+采样60+去10大）1164.802us，ratio=0.776≤1.2。</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>约 2.1 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TC_PF_002 / gqa_decode_kv32k</t>
@@ -706,7 +732,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_msprof_gqa_decode_kv32k.png</t>
+          <t>见嵌入图 / figures/perf_msprof_gqa_decode_kv32k.png</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
@@ -717,16 +743,16 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>msprof=9153.690us，ratio=0.987≤1.2。chrono=9177.967us。</t>
+          <t>msprof task_time（预热10+采样60+去10大）9153.69us，ratio=0.987≤1.2。</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>约 16.5 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TC_PF_003 / gqa_decode_kv128k</t>
@@ -754,7 +780,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_msprof_gqa_decode_kv128k.png</t>
+          <t>见嵌入图 / figures/perf_msprof_gqa_decode_kv128k.png</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -765,16 +791,16 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>msprof=36404.275us，ratio=1.020≤1.2。chrono=36436.364us。</t>
+          <t>msprof task_time（预热10+采样60+去10大）36404.275us，ratio=1.020≤1.2。</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>约 66 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TC_PF_004 / gqa_prefill_kv4k</t>
@@ -802,7 +828,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_msprof_gqa_prefill_kv4k.png</t>
+          <t>见嵌入图 / figures/perf_msprof_gqa_prefill_kv4k.png</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -813,16 +839,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>msprof=21917.734us，ratio=0.288≤1.2。chrono=21961.653us。</t>
+          <t>msprof task_time（预热10+采样60+去10大）21917.734us，ratio=0.288≤1.2。</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>约 258 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TC_PF_005 / gqa_prefill_kv32k</t>
@@ -850,7 +876,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_msprof_gqa_prefill_kv32k.png</t>
+          <t>见嵌入图 / figures/perf_msprof_gqa_prefill_kv32k.png</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -861,16 +887,16 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>任务书未给 baseline，按 kv4k×8 外推 607874.024。msprof=170370.761us，ratio=0.280≤1.2。chrono=170334.046us。</t>
+          <t>msprof task_time（预热10+采样60+去10大）170370.761us，ratio=0.280≤1.2。 任务书未给 baseline，按 kv4k×8 外推。</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>约 2.0 GiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>性能测试总计</t>
@@ -878,7 +904,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>任务书 5 条 shape；官方 msprof 口径</t>
+          <t>任务书 5 条；msprof 口径</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -898,7 +924,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>/root/验收交付件/figures/perf_chrono.png；/root/验收交付件/figures/perf_ratio_bar.png；/root/验收交付件/figures/perf_latency_cmp.png</t>
+          <t>figures/perf_ratio_bar.png</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -913,43 +939,67 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>5 条均 ≤1.2× Full-QK。msprof：1164.802 / 9153.690 / 36404.275 / 21917.734 / 170370.761 us。</t>
+          <t>5 条均 ≤1.2× Full-QK：1164.802 / 9153.690 / 36404.275 / 21917.734 / 170370.761 us。</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>见上五条</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="60" customHeight="1">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>说明：官方模板「TBE算子性能」列，本算子无 TBE，改填任务书 Paged Full-QK 标杆(us)；「Ascend C算子性能」填 msprof task_time 均值。复现：msprof --ai-core=on --task-time=on --application="/root/backup/bench_aclnn_perf &lt;case&gt;"；chrono 对照 /root/backup/bench_aclnn_perf。仓分支 feat/turbo_quant_attention_score commit 72bb444f。截图粘贴到「Ascend截图」列。</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
+          <t>「Full-QK标杆」列为任务书 Paged Full-QK baseline；「Ascend C」为 msprof。复现：msprof --ai-core=on --task-time=on --application="/root/backup/bench_aclnn_perf &lt;case&gt;"。commit 9c168855。</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A12:J14"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>